--- a/Result/profitability/2247.xlsx
+++ b/Result/profitability/2247.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2247</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11671</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10343</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1328</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="G38" t="n">
+        <v>410</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>426</v>
+      </c>
+      <c r="K38" t="n">
+        <v>339</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11.3325</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.7872340425531914</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.04849498327759194</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.3236714975845411</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.2800000000000011</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.02522522522522541</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
